--- a/data/trans_orig/IP07C20-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C20-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22389</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36783</t>
+          <t>36988</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23275</t>
+          <t>22699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37894</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49640</t>
+          <t>49463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69829</t>
+          <t>70588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35005</t>
+          <t>35873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52475</t>
+          <t>52266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47494</t>
+          <t>47980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64939</t>
+          <t>65114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88217</t>
+          <t>88289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112219</t>
+          <t>112167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27154</t>
+          <t>26665</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43750</t>
+          <t>42460</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21686</t>
+          <t>21214</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>35227</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52596</t>
+          <t>52147</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73408</t>
+          <t>73221</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14016</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26985</t>
+          <t>27180</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44058</t>
+          <t>43557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40385</t>
+          <t>40830</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60040</t>
+          <t>59729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71543</t>
+          <t>71793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97120</t>
+          <t>97355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79661</t>
+          <t>78807</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100340</t>
+          <t>100434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59365</t>
+          <t>58884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80111</t>
+          <t>79901</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142875</t>
+          <t>144236</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173276</t>
+          <t>176014</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33969</t>
+          <t>33920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51777</t>
+          <t>52135</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>51717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71259</t>
+          <t>73182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91200</t>
+          <t>90830</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120316</t>
+          <t>117938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14788</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52546</t>
+          <t>51938</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75199</t>
+          <t>75725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67399</t>
+          <t>67406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92690</t>
+          <t>92827</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127934</t>
+          <t>127119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160549</t>
+          <t>160531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118824</t>
+          <t>118809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146235</t>
+          <t>147012</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112363</t>
+          <t>111760</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139751</t>
+          <t>140026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>237900</t>
+          <t>240181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278224</t>
+          <t>278679</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66036</t>
+          <t>66049</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91705</t>
+          <t>90556</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77127</t>
+          <t>76117</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103249</t>
+          <t>101520</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>147749</t>
+          <t>149753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>184743</t>
+          <t>185089</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18012</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>30480</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2012 (tasa de respuesta: 95,31%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2012 (tasa de respuesta: 95,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48762</t>
+          <t>48358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68138</t>
+          <t>69362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41159</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59844</t>
+          <t>59341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93861</t>
+          <t>95495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121869</t>
+          <t>122799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41520</t>
+          <t>40663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60480</t>
+          <t>60137</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43324</t>
+          <t>42812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62217</t>
+          <t>62970</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89461</t>
+          <t>88365</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116206</t>
+          <t>116227</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>25318</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41501</t>
+          <t>42550</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28928</t>
+          <t>27315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46132</t>
+          <t>45300</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58417</t>
+          <t>57676</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81722</t>
+          <t>81264</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14942</t>
+          <t>15867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46925</t>
+          <t>46354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66228</t>
+          <t>66955</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>52475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73541</t>
+          <t>73095</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102689</t>
+          <t>102775</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131882</t>
+          <t>132327</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51220</t>
+          <t>51370</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70987</t>
+          <t>71544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53056</t>
+          <t>54124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74596</t>
+          <t>73824</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110541</t>
+          <t>110332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139048</t>
+          <t>139460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29103</t>
+          <t>29189</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>46605</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25019</t>
+          <t>25016</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41396</t>
+          <t>41513</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>59844</t>
+          <t>60035</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83047</t>
+          <t>83978</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14589</t>
+          <t>15245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101240</t>
+          <t>100830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128582</t>
+          <t>129665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98207</t>
+          <t>96875</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125520</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207350</t>
+          <t>208182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247499</t>
+          <t>247271</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97198</t>
+          <t>98393</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125743</t>
+          <t>124808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102862</t>
+          <t>101628</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130872</t>
+          <t>130403</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>206826</t>
+          <t>207188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>247382</t>
+          <t>245751</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58621</t>
+          <t>58727</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84000</t>
+          <t>83714</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58223</t>
+          <t>58355</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82630</t>
+          <t>82342</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122312</t>
+          <t>123759</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156617</t>
+          <t>156875</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25285</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21165</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>36613</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56226</t>
+          <t>56136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37621</t>
+          <t>37350</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56358</t>
+          <t>56726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79740</t>
+          <t>79844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106497</t>
+          <t>107165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46097</t>
+          <t>46195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67567</t>
+          <t>67521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59319</t>
+          <t>58429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81297</t>
+          <t>80173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110598</t>
+          <t>110086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139590</t>
+          <t>140719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>41942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62701</t>
+          <t>61476</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36270</t>
+          <t>37052</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55787</t>
+          <t>56014</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84455</t>
+          <t>83965</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111545</t>
+          <t>112184</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24058</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20499</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>11763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21342</t>
+          <t>22124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35437</t>
+          <t>35418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53919</t>
+          <t>54356</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32604</t>
+          <t>32760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51921</t>
+          <t>50813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71855</t>
+          <t>71797</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100473</t>
+          <t>99862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44714</t>
+          <t>43290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64555</t>
+          <t>64734</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52125</t>
+          <t>51600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73709</t>
+          <t>72739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101560</t>
+          <t>100278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132970</t>
+          <t>131048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38711</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58590</t>
+          <t>59425</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41608</t>
+          <t>41385</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62102</t>
+          <t>61259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86258</t>
+          <t>86558</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>113344</t>
+          <t>114985</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20207</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35819</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>729</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>77235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105898</t>
+          <t>103648</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74724</t>
+          <t>73514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102420</t>
+          <t>101442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161167</t>
+          <t>159706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198240</t>
+          <t>198572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95880</t>
+          <t>96745</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126221</t>
+          <t>124864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115819</t>
+          <t>116574</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145904</t>
+          <t>146837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220606</t>
+          <t>220546</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>261094</t>
+          <t>261124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85981</t>
+          <t>87073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114152</t>
+          <t>115098</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84717</t>
+          <t>83909</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112882</t>
+          <t>110979</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>178407</t>
+          <t>178874</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>215090</t>
+          <t>217021</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32874</t>
+          <t>32753</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>43077</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66899</t>
+          <t>66043</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>31267</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C20-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C20-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el/la menor en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30165</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22584</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39147</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,29%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>28954</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22208</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36988</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22153</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36960</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25,92%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>30165</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>22699</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38047</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>24,43%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49463</t>
+          <t>48949</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70588</t>
+          <t>71078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47511</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>65318</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>45,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43371</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35873</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52266</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>34905</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52126</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,82%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56258</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>47980</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>65114</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88289</t>
+          <t>87668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112167</t>
+          <t>111840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27977</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20792</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35821</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>22,66%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>29,01%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>34588</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>26665</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>42460</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>26497</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>42831</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>30,96%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>23,87%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>38,01%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>27977</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21214</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>35227</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>22,66%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52147</t>
+          <t>52416</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73221</t>
+          <t>72971</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5900</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2666</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2661</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6184</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6964</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5900</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2652</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10690</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14325</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1146</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6897</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2136</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5711</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5622</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3181</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6811</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49635</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40279</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>59345</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>34545</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27180</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43557</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>26946</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>44556</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>19,31%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>49635</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>40830</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>59729</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>26,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71793</t>
+          <t>71927</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97355</t>
+          <t>98601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69337</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59423</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>79266</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>89143</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78807</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>100434</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>78127</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>100239</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>49,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>56,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69337</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>58884</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>79901</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144236</t>
+          <t>143496</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176014</t>
+          <t>176062</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61432</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>51330</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70682</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>33,01%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>27,58%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>37,98%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>42924</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>33920</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>52135</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>34014</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>52768</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>23,99%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>18,96%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>29,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>61432</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>51717</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73182</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>33,01%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90830</t>
+          <t>90984</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>117938</t>
+          <t>119369</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4542</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8615</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9048</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5218</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14856</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5188</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15536</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4542</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8908</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>20537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3896</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3275</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8017</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7127</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1151</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4567</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>79801</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>67944</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>92189</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>25,78%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21,95%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>29,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>63499</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>51938</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>75725</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>52772</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>75386</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>21,85%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,87%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>79801</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>67406</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>92827</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>25,78%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127119</t>
+          <t>127807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160531</t>
+          <t>159720</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>125595</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>111547</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>140030</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,23%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>132513</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>118809</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>147012</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>118815</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>146668</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>45,59%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>40,88%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>50,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>125595</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>111760</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>140026</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>40,57%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>36,1%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>240181</t>
+          <t>237790</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278679</t>
+          <t>277509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>89409</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>76401</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>102186</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>28,88%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>24,68%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>33,01%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>77512</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>66049</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>90556</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>65106</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>90237</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>26,67%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>22,73%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>89409</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>76117</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>101520</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>149753</t>
+          <t>150300</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>185089</t>
+          <t>185031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10442</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6426</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17032</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>11710</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>7394</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>18501</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7191</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>18451</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>10442</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>5851</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>16670</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4332</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8176</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>5412</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2670</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10217</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>10406</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>4332</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1882</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>9139</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>309578</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>432</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>309578</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2012 (tasa de respuesta: 95,31%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el/la menor en 2012 (tasa de respuesta: 95,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49855</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40363</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>60318</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,08%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>38,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>58349</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>48358</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>69362</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>49506</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>68193</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>49855</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>39989</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>59341</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>32,21%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95495</t>
+          <t>95412</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122799</t>
+          <t>122027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -3111,107 +3111,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52447</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43099</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>62656</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,88%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>50246</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>40663</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>60137</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40893</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>59799</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>33,88%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>40,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>52447</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>42812</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62970</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>27,57%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>40,32%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>102692</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>90303</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>118080</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>33,88%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>40,68%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>102692</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>88365</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>116227</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>33,88%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36465</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28333</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>45376</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>18,31%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>29,32%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32795</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25318</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>42550</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>25124</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>42677</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>22,11%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>28,69%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>36465</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>27315</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>45300</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>23,56%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57676</t>
+          <t>56954</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81264</t>
+          <t>81372</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8933</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15505</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4969</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9838</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10163</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,35%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8933</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4667</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15675</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3650</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13192</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1963</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6233</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7081</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3535</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>12701</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154780</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154780</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154780</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>148323</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>148323</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>148323</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154780</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154780</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154780</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>62419</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>52059</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>71948</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>55980</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46354</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>66955</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>46594</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>66202</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,66%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>41,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>62419</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>52475</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>73095</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>36,58%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102775</t>
+          <t>103092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132327</t>
+          <t>132659</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>63179</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53226</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>73924</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>60909</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>51370</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>71544</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>51421</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>71298</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>63179</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>54124</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>73824</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110332</t>
+          <t>110473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139460</t>
+          <t>139899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33131</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>25724</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>42583</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19,41%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37649</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29189</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>46605</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>29408</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>47324</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>23,31%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>18,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>28,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>33131</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>25016</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>41513</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60035</t>
+          <t>59691</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83978</t>
+          <t>84064</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8944</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4987</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14778</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5664</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10799</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2637</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11320</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8944</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5119</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15245</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>21140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2977</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7239</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4646</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4367</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2977</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7483</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>161508</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>161508</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>161508</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>112274</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>99867</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>126577</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>34,5%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>38,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>114329</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>100830</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>129665</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>101456</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>129117</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>36,9%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41,85%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>112274</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>96875</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>127108</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>34,5%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>208182</t>
+          <t>206511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247271</t>
+          <t>247015</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>115626</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>101068</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>129298</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,53%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>111154</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>98393</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>124808</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>97295</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>124199</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,88%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,76%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>115626</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>101628</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>130403</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,53%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207188</t>
+          <t>205824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>245751</t>
+          <t>246784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>69596</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>58913</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>82731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>21,39%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>18,1%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>70444</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>58727</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>83714</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>59350</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>83069</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>22,74%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>27,02%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>69596</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>58355</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>82342</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>21,39%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123759</t>
+          <t>122926</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156875</t>
+          <t>158762</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17876</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11853</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>26895</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>10634</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>17782</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>17261</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>17876</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>11512</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>25287</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>20269</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38268</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10058</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>17455</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>3269</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7415</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7263</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>10058</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>5745</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>16875</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>325431</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>325431</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>325431</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>309831</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>309831</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>309831</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>325431</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>325431</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>325431</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el/la menor en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46454</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37241</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>56840</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,85%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>45827</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36613</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>56136</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36704</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>56574</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25,56%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>46454</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>37350</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>56726</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>26,01%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79844</t>
+          <t>79106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107165</t>
+          <t>106635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>69350</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59854</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80975</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>56446</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46195</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67521</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47041</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67320</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,48%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,66%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>69350</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58429</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80173</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>38,83%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110086</t>
+          <t>111734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140719</t>
+          <t>142310</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>45885</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36795</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56061</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>25,69%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>31,39%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>51888</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>41942</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>61476</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>42376</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>63038</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>28,94%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>23,39%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>34,29%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>45885</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>37052</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>56014</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>25,69%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83965</t>
+          <t>84001</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112184</t>
+          <t>112399</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11094</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6650</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17303</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16534</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10994</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23952</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10738</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23097</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11094</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6540</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16833</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>19889</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35986</t>
+          <t>36357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2862</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11175</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>8608</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4697</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14124</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4699</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>14554</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5827</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2779</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11763</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22124</t>
+          <t>21803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>179303</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>179303</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>179303</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>41394</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31851</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>50695</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>43930</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35418</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54356</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34766</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>53451</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>26,76%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>41394</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>32760</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>50813</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71797</t>
+          <t>72409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99862</t>
+          <t>99910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>61633</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>51166</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>72749</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>54006</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>43290</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>64734</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>44010</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>64545</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>32,9%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,44%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>61633</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>51600</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>72739</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,13%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100278</t>
+          <t>101830</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131048</t>
+          <t>130881</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>51543</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41932</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>62311</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>30,21%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>24,58%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>36,53%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>48298</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>38711</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>59425</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>39513</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>58701</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>29,42%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>36,2%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>51543</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>41385</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>61259</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>30,21%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86558</t>
+          <t>86787</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114985</t>
+          <t>114120</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13101</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8008</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19995</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>12685</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7688</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19234</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7765</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19321</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13101</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8395</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21042</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34637</t>
+          <t>35786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2920</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7501</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5226</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2284</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11107</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2168</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10088</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,18%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2920</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7689</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164145</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164145</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164145</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>87849</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>75051</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>101967</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>25,16%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>29,2%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>89756</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>77235</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>103648</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>76796</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>104190</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>26,13%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>87849</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>73514</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>101442</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>159706</t>
+          <t>159004</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198572</t>
+          <t>196899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -6751,74 +6751,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>130983</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>117381</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>146351</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>110452</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>96745</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>124864</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>96061</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>124869</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>32,16%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>36,36%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>130983</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>116574</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>146837</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,51%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>33,38%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>338</t>
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220546</t>
+          <t>222056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>261124</t>
+          <t>264988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,26%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>97429</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>84638</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>112712</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>27,9%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>24,24%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>32,28%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>100186</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>87073</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115098</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>86326</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>113548</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>29,17%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>25,35%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>97429</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>83909</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>110979</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>27,9%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>178874</t>
+          <t>177142</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>217021</t>
+          <t>218364</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>24195</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17274</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>33762</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>29220</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>21715</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>38419</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>21390</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>38762</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>8,51%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,32%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>24195</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>16626</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>32753</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43077</t>
+          <t>43252</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66043</t>
+          <t>67489</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8746</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4623</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14604</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>13833</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>8514</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>20070</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>8566</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>21149</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>8746</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>4388</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>14805</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15747</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31267</t>
+          <t>31241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>490</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>343448</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>343448</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>343448</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
